--- a/uploads/excel/Apartment_Import_Template.xlsx
+++ b/uploads/excel/Apartment_Import_Template.xlsx
@@ -69,7 +69,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -114,11 +114,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -126,6 +141,9 @@
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -585,7 +603,7 @@
       <c r="I2" s="4" t="str">
         <v>john@test.com</v>
       </c>
-      <c r="J2" s="4" t="str">
+      <c r="J2" s="5" t="str">
         <v>123456789012</v>
       </c>
       <c r="K2" s="4" t="str">
